--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/elder_exile.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/elder_exile.xlsx
@@ -191,7 +191,7 @@
   <si>
     <t xml:space="preserve">キキキ…さて、どこから話すべきか。
 この村の南東にルーリエという神殿があるのを、汝は知っているか？　神々が地上から去り、今はもう海の底に沈んだ哀しきルーリエ…その神殿で、我は暮らしていたのだ。かつて、まだ人間だった頃な。
-神殿には、どこからか迷い混んだ大食いトドの子が一匹いて、我になついていた。名はデュポンヌといい、愚かしいほど食い意地の張ったやつだったが…キキキ…あの鈍重で愛らしい獣に、我は奇妙なほど情を注いでいたものだ。</t>
+神殿には、どこからか迷い込んだ大食いトドの子が一匹いて、我になついていた。名はデュポンヌといい、愚かしいほど食い意地の張ったやつだったが…キキキ…あの鈍重で愛らしい獣に、我は奇妙なほど情を注いでいたものだ。</t>
   </si>
   <si>
     <t xml:space="preserve">Keh keh keh... Now, where to begin?
